--- a/ITRI611_2022_Project_Submission_1.xlsx
+++ b/ITRI611_2022_Project_Submission_1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NWUNextcloud\Susan\ITRI611\2022\Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Llewellyn\Desktop\DW2022_Repo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD81FDF-68D0-4FAC-AE2E-E1C8D99D0C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CED41E8-BDFA-41A1-8740-38AD7EF8B35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1890" windowWidth="29040" windowHeight="15840" tabRatio="827" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12696" tabRatio="827" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Start Here" sheetId="1" r:id="rId1"/>
@@ -927,19 +927,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultColWidth="18.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="18.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="143.85546875" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="18.28515625" style="1"/>
+    <col min="1" max="1" width="22.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="143.88671875" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="18.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="18" customFormat="1" ht="20.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="18" customFormat="1" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="18" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="90.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="87" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -947,7 +947,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>70</v>
       </c>
@@ -955,7 +955,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -963,17 +963,17 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="20" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
@@ -981,7 +981,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="150" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="144" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -989,7 +989,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>4</v>
       </c>
@@ -997,7 +997,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1021,18 +1021,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" style="3" customWidth="1"/>
     <col min="3" max="3" width="22" style="3" customWidth="1"/>
-    <col min="4" max="6" width="39.7109375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="6.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="3"/>
+    <col min="4" max="6" width="39.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="6.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B1" s="6"/>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -1045,7 +1045,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>6</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="11"/>
       <c r="B3" s="9" t="s">
         <v>7</v>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H3" s="10"/>
     </row>
-    <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="11"/>
       <c r="B4" s="9" t="s">
         <v>9</v>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="H4" s="10"/>
     </row>
-    <row r="5" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A5" s="11"/>
       <c r="B5" s="9" t="s">
         <v>15</v>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="H5" s="10"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>17</v>
       </c>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:8" ht="150" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
       <c r="B7" s="14" t="s">
         <v>21</v>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="H7" s="10"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="11"/>
       <c r="B8" s="14" t="s">
         <v>22</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H8" s="10"/>
     </row>
-    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>67</v>
       </c>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:8" ht="120" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>61</v>
       </c>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H10" s="10"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="11"/>
       <c r="B11" s="9" t="s">
         <v>63</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="H11" s="10"/>
     </row>
-    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>68</v>
       </c>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>64</v>
       </c>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="H13" s="10"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="11"/>
       <c r="B14" s="9" t="s">
         <v>66</v>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="H14" s="10"/>
     </row>
-    <row r="15" spans="1:8" s="15" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" s="15" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>25</v>
       </c>
@@ -1380,99 +1380,99 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultColWidth="19" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="19" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19" style="19"/>
     <col min="2" max="2" width="19" style="3"/>
     <col min="3" max="16384" width="19" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" s="19" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B4" s="19" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B5" s="19" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" s="19" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C7" s="19" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C8" s="19" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C9" s="19" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C10" s="19" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C11" s="19" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B12" s="19" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C13" s="19" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C14" s="19" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C15" s="19" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C16" s="19" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" s="19" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C18" s="19" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C19" s="19" t="s">
         <v>51</v>
       </c>
